--- a/AAII_Financials/Quarterly/LGCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
   <si>
     <t>LGCB</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,146 +656,196 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>9000</v>
+        <v>2400</v>
       </c>
       <c r="E8" s="3">
-        <v>22000</v>
+        <v>2400</v>
       </c>
       <c r="F8" s="3">
-        <v>8400</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>1900</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H8" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>6800</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>7100</v>
+        <v>2000</v>
       </c>
       <c r="E9" s="3">
-        <v>18300</v>
+        <v>2000</v>
       </c>
       <c r="F9" s="3">
-        <v>6700</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>1900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>5800</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1900</v>
+        <v>400</v>
       </c>
       <c r="E10" s="3">
-        <v>3700</v>
+        <v>400</v>
       </c>
       <c r="F10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -807,37 +857,53 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="G12" s="3">
+        <v>200</v>
+      </c>
+      <c r="H12" s="3">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3">
+        <v>100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>200</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -865,28 +931,40 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -894,8 +972,20 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -923,8 +1013,20 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -933,66 +1035,94 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8200</v>
+        <v>3200</v>
       </c>
       <c r="E17" s="3">
-        <v>20600</v>
+        <v>3200</v>
       </c>
       <c r="F17" s="3">
-        <v>7700</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>2500</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J17" s="3">
+        <v>6500</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>800</v>
+        <v>-800</v>
       </c>
       <c r="E18" s="3">
-        <v>1400</v>
+        <v>-800</v>
       </c>
       <c r="F18" s="3">
-        <v>700</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-700</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>300</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1004,8 +1134,12 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1013,144 +1147,204 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>800</v>
+        <v>-800</v>
       </c>
       <c r="E21" s="3">
-        <v>1500</v>
+        <v>-800</v>
       </c>
       <c r="F21" s="3">
-        <v>800</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-700</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>800</v>
+        <v>-800</v>
       </c>
       <c r="E23" s="3">
-        <v>1500</v>
+        <v>-800</v>
       </c>
       <c r="F23" s="3">
-        <v>800</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>-800</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H23" s="3">
+        <v>400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>300</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
-        <v>400</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
-        <v>200</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
+        <v>100</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1178,66 +1372,102 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>600</v>
+        <v>-700</v>
       </c>
       <c r="E26" s="3">
-        <v>1100</v>
+        <v>-700</v>
       </c>
       <c r="F26" s="3">
-        <v>600</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>-600</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H26" s="3">
+        <v>300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>300</v>
+      </c>
+      <c r="J26" s="3">
+        <v>200</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>600</v>
+        <v>-700</v>
       </c>
       <c r="E27" s="3">
-        <v>1100</v>
+        <v>-700</v>
       </c>
       <c r="F27" s="3">
-        <v>600</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>-600</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H27" s="3">
+        <v>300</v>
+      </c>
+      <c r="I27" s="3">
+        <v>300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>200</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1265,8 +1495,20 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1294,8 +1536,20 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1323,8 +1577,20 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1352,8 +1618,20 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1361,57 +1639,81 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>600</v>
+        <v>-700</v>
       </c>
       <c r="E33" s="3">
-        <v>1100</v>
+        <v>-700</v>
       </c>
       <c r="F33" s="3">
-        <v>600</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>-600</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H33" s="3">
+        <v>300</v>
+      </c>
+      <c r="I33" s="3">
+        <v>300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>200</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1439,71 +1741,107 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>600</v>
+        <v>-700</v>
       </c>
       <c r="E35" s="3">
-        <v>1100</v>
+        <v>-700</v>
       </c>
       <c r="F35" s="3">
-        <v>600</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>-600</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H35" s="3">
+        <v>300</v>
+      </c>
+      <c r="I35" s="3">
+        <v>300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>200</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1515,8 +1853,12 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1528,240 +1870,340 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H41" s="3">
         <v>3500</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="I41" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3700</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H43" s="3">
         <v>2900</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="I43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J43" s="3">
+        <v>2700</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
         <v>100</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+      <c r="E44" s="3">
+        <v>100</v>
+      </c>
+      <c r="F44" s="3">
+        <v>700</v>
+      </c>
+      <c r="G44" s="3">
+        <v>700</v>
+      </c>
+      <c r="H44" s="3">
+        <v>100</v>
+      </c>
+      <c r="I44" s="3">
+        <v>100</v>
+      </c>
+      <c r="J44" s="3">
+        <v>300</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2600</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>5200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>100</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>11900</v>
+      </c>
+      <c r="F46" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G46" s="3">
+        <v>9600</v>
+      </c>
+      <c r="H46" s="3">
         <v>9200</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="I46" s="3">
+        <v>9200</v>
+      </c>
+      <c r="J46" s="3">
+        <v>7100</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>200</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+      <c r="I47" s="3">
+        <v>200</v>
+      </c>
+      <c r="J47" s="3">
+        <v>100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>800</v>
+      </c>
+      <c r="F48" s="3">
+        <v>800</v>
+      </c>
+      <c r="G48" s="3">
+        <v>800</v>
+      </c>
+      <c r="H48" s="3">
         <v>1400</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="I48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1800</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1789,8 +2231,20 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1818,8 +2272,20 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1847,37 +2313,61 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>100</v>
+      </c>
+      <c r="F52" s="3">
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
+        <v>100</v>
+      </c>
+      <c r="H52" s="3">
+        <v>100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1905,37 +2395,61 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13100</v>
+      </c>
+      <c r="F54" s="3">
+        <v>10600</v>
+      </c>
+      <c r="G54" s="3">
+        <v>10600</v>
+      </c>
+      <c r="H54" s="3">
         <v>11100</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+      <c r="I54" s="3">
+        <v>11100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>9100</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1947,8 +2461,12 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1960,158 +2478,222 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="E57" s="3">
+        <v>800</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H57" s="3">
+        <v>800</v>
+      </c>
+      <c r="I57" s="3">
+        <v>800</v>
+      </c>
+      <c r="J57" s="3">
+        <v>500</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>600</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>800</v>
+      </c>
+      <c r="J58" s="3">
+        <v>700</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2100</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>2200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1000</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F60" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G60" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="I60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>3700</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1000</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>3</v>
@@ -2134,8 +2716,20 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2163,8 +2757,20 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2192,8 +2798,20 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2221,37 +2839,61 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F66" s="3">
+        <v>7100</v>
+      </c>
+      <c r="G66" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H66" s="3">
         <v>6400</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="I66" s="3">
+        <v>6400</v>
+      </c>
+      <c r="J66" s="3">
+        <v>6300</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2263,8 +2905,12 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2292,8 +2938,20 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2321,8 +2979,20 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2350,8 +3020,20 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2379,37 +3061,61 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>700</v>
+      </c>
+      <c r="F72" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G72" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H72" s="3">
         <v>3300</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="I72" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J72" s="3">
+        <v>2700</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2437,8 +3143,20 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2466,8 +3184,20 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2495,37 +3225,61 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G76" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H76" s="3">
         <v>4800</v>
       </c>
-      <c r="E76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="I76" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J76" s="3">
+        <v>2700</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2553,71 +3307,107 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>600</v>
+        <v>-700</v>
       </c>
       <c r="E81" s="3">
-        <v>1100</v>
+        <v>-700</v>
       </c>
       <c r="F81" s="3">
-        <v>600</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>-600</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H81" s="3">
+        <v>300</v>
+      </c>
+      <c r="I81" s="3">
+        <v>300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>200</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2629,13 +3419,17 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -2643,14 +3437,14 @@
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -2658,8 +3452,20 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2687,8 +3493,20 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2716,8 +3534,20 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2745,8 +3575,20 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2774,8 +3616,20 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2803,37 +3657,61 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="E89" s="3">
-        <v>1200</v>
+        <v>-1900</v>
       </c>
       <c r="F89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>-1000</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J89" s="3">
+        <v>700</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2845,16 +3723,20 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -2874,8 +3756,20 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2903,8 +3797,20 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2932,37 +3838,61 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E94" s="3">
-        <v>700</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F94" s="3">
-        <v>800</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H94" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I94" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2974,37 +3904,53 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3032,8 +3978,20 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3061,8 +4019,20 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3090,42 +4060,66 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-200</v>
+        <v>2100</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F100" s="3">
-        <v>-800</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>400</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
@@ -3133,14 +4127,14 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -3148,33 +4142,57 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-200</v>
+        <v>200</v>
       </c>
       <c r="E102" s="3">
-        <v>1900</v>
+        <v>200</v>
       </c>
       <c r="F102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>-1200</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J102" s="3">
+        <v>1000</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>LGCB</t>
   </si>
@@ -656,62 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,38 +723,44 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F8" s="3">
         <v>2400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>4500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>4500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>6800</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -762,38 +770,44 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="3">
         <v>2000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>5800</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,37 +817,43 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F10" s="3">
         <v>400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>400</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
       <c r="H10" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
+      <c r="K10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1000</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
@@ -844,8 +864,14 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,38 +887,40 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -902,8 +930,14 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -943,8 +977,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -954,24 +994,24 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -984,8 +1024,14 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1025,8 +1071,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1039,38 +1091,40 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="3">
         <v>3200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6500</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,37 +1134,43 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>300</v>
       </c>
       <c r="J18" s="3">
         <v>300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
+      <c r="K18" s="3">
+        <v>300</v>
+      </c>
+      <c r="L18" s="3">
+        <v>300</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
@@ -1121,8 +1181,14 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1138,8 +1204,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1164,11 +1232,11 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1179,38 +1247,44 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1220,8 +1294,14 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1246,11 +1326,11 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1261,16 +1341,22 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-800</v>
+        <v>900</v>
       </c>
       <c r="E23" s="3">
-        <v>-800</v>
+        <v>900</v>
       </c>
       <c r="F23" s="3">
         <v>-800</v>
@@ -1279,20 +1365,20 @@
         <v>-800</v>
       </c>
       <c r="H23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J23" s="3">
         <v>400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>300</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1302,37 +1388,43 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
+        <v>100</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1343,8 +1435,14 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1384,38 +1482,44 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>200</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,38 +1529,44 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>200</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1466,8 +1576,14 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1507,8 +1623,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1548,8 +1670,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1589,8 +1717,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1630,8 +1764,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1656,11 +1796,11 @@
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1671,38 +1811,44 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>200</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,8 +1858,14 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1753,38 +1905,44 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>200</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1794,43 +1952,49 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1840,8 +2004,14 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1857,8 +2027,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1874,38 +2046,40 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3700</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1915,16 +2089,22 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E42" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F42" s="3">
         <v>200</v>
@@ -1933,20 +2113,20 @@
         <v>200</v>
       </c>
       <c r="H42" s="3">
+        <v>200</v>
+      </c>
+      <c r="I42" s="3">
+        <v>200</v>
+      </c>
+      <c r="J42" s="3">
         <v>100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>200</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -1956,38 +2136,44 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F43" s="3">
         <v>3000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2700</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1997,8 +2183,14 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2009,26 +2201,26 @@
         <v>100</v>
       </c>
       <c r="F44" s="3">
+        <v>100</v>
+      </c>
+      <c r="G44" s="3">
+        <v>100</v>
+      </c>
+      <c r="H44" s="3">
         <v>700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>300</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2038,38 +2230,44 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>500</v>
+      </c>
+      <c r="F45" s="3">
         <v>5200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>5200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>5100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2079,38 +2277,44 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F46" s="3">
         <v>11900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>9600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>9600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>9200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>9200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2120,8 +2324,14 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2137,21 +2347,21 @@
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2161,16 +2371,22 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F48" s="3">
         <v>800</v>
@@ -2179,20 +2395,20 @@
         <v>800</v>
       </c>
       <c r="H48" s="3">
+        <v>800</v>
+      </c>
+      <c r="I48" s="3">
+        <v>800</v>
+      </c>
+      <c r="J48" s="3">
         <v>1400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1800</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2202,8 +2418,14 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2243,8 +2465,14 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2284,8 +2512,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2325,16 +2559,22 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>100</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -2351,11 +2591,11 @@
       <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3">
+        <v>100</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -2366,8 +2606,14 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2407,38 +2653,44 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F54" s="3">
         <v>13100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>10600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>10600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>11100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9100</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,8 +2700,14 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2465,8 +2723,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2482,38 +2742,40 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2523,38 +2785,44 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F58" s="3">
         <v>800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2564,38 +2832,44 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F59" s="3">
         <v>2200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2605,38 +2879,44 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F60" s="3">
         <v>5400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,38 +2926,44 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F61" s="3">
         <v>1500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2687,8 +2973,14 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2728,8 +3020,14 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2769,8 +3067,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2810,8 +3114,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2851,38 +3161,44 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F66" s="3">
         <v>6800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>7100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2892,8 +3208,14 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2909,8 +3231,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2950,8 +3274,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2991,8 +3321,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3032,8 +3368,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3073,38 +3415,44 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F72" s="3">
         <v>700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2700</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3114,8 +3462,14 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3155,8 +3509,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3196,8 +3556,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3237,38 +3603,44 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F76" s="3">
         <v>6200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2700</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3278,8 +3650,14 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3319,43 +3697,49 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3365,38 +3749,44 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>200</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3406,8 +3796,14 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3423,8 +3819,10 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3435,10 +3833,10 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
@@ -3446,11 +3844,11 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3464,8 +3862,14 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3505,8 +3909,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3546,8 +3956,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3587,8 +4003,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3628,8 +4050,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3669,38 +4097,44 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>700</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3710,8 +4144,14 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3727,8 +4167,10 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3738,11 +4180,11 @@
       <c r="E91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -3768,8 +4210,14 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3809,8 +4257,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3850,37 +4304,43 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>1000</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -3891,8 +4351,14 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3908,8 +4374,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3934,11 +4402,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -3949,8 +4417,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3990,8 +4464,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4031,8 +4511,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4072,22 +4558,28 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F100" s="3">
         <v>2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2100</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-100</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
@@ -4096,14 +4588,14 @@
         <v>-100</v>
       </c>
       <c r="J100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4113,34 +4605,40 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -4154,38 +4652,44 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>300</v>
+      </c>
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4193,6 +4697,12 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
   <si>
     <t>LGCB</t>
   </si>
@@ -656,70 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -729,44 +730,50 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F8" s="3">
         <v>2700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>6800</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -776,44 +783,50 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>400</v>
+      </c>
+      <c r="F9" s="3">
         <v>1000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>5800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,43 +836,49 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F10" s="3">
         <v>1700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>400</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3">
         <v>1000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1000</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
@@ -870,8 +889,14 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,44 +914,46 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,8 +963,14 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,8 +1016,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1000,24 +1039,24 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1030,8 +1069,14 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1077,8 +1122,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1093,44 +1144,46 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F17" s="3">
         <v>2000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6500</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1140,43 +1193,49 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F18" s="3">
         <v>700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>300</v>
-      </c>
-      <c r="K18" s="3">
-        <v>300</v>
       </c>
       <c r="L18" s="3">
         <v>300</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
+      <c r="M18" s="3">
+        <v>300</v>
+      </c>
+      <c r="N18" s="3">
+        <v>300</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
@@ -1187,8 +1246,14 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1206,16 +1271,18 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1238,11 +1305,11 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1253,44 +1320,50 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1300,16 +1373,22 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1332,11 +1411,11 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
@@ -1347,22 +1426,28 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F23" s="3">
         <v>900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-800</v>
       </c>
       <c r="H23" s="3">
         <v>-800</v>
@@ -1371,20 +1456,20 @@
         <v>-800</v>
       </c>
       <c r="J23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L23" s="3">
         <v>400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>300</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1394,43 +1479,49 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>200</v>
+      </c>
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>100</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
+        <v>100</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1441,8 +1532,14 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1488,44 +1585,50 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F26" s="3">
         <v>500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>200</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1535,44 +1638,50 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>200</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1582,8 +1691,14 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1629,8 +1744,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1676,8 +1797,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1723,8 +1850,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1770,16 +1903,22 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1802,11 +1941,11 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1817,44 +1956,50 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>200</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,8 +2009,14 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1911,44 +2062,50 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>200</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1958,49 +2115,55 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2010,8 +2173,14 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2029,8 +2198,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2048,44 +2219,46 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>300</v>
+      </c>
+      <c r="F41" s="3">
         <v>2000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3700</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,22 +2268,28 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>200</v>
+      </c>
+      <c r="F42" s="3">
         <v>400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>400</v>
-      </c>
-      <c r="F42" s="3">
-        <v>200</v>
-      </c>
-      <c r="G42" s="3">
-        <v>200</v>
       </c>
       <c r="H42" s="3">
         <v>200</v>
@@ -2119,20 +2298,20 @@
         <v>200</v>
       </c>
       <c r="J42" s="3">
+        <v>200</v>
+      </c>
+      <c r="K42" s="3">
+        <v>200</v>
+      </c>
+      <c r="L42" s="3">
         <v>100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>200</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -2142,44 +2321,50 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>16100</v>
+      </c>
+      <c r="F43" s="3">
         <v>7100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>7100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2700</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2189,16 +2374,22 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F44" s="3">
         <v>100</v>
@@ -2207,26 +2398,26 @@
         <v>100</v>
       </c>
       <c r="H44" s="3">
+        <v>100</v>
+      </c>
+      <c r="I44" s="3">
+        <v>100</v>
+      </c>
+      <c r="J44" s="3">
         <v>700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>300</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2236,44 +2427,50 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>5200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>5100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,44 +2480,50 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F46" s="3">
         <v>12000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>12000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>11900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>11900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>9600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>9600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>9200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2330,8 +2533,14 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2353,21 +2562,21 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2377,22 +2586,28 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>600</v>
+      </c>
+      <c r="F48" s="3">
         <v>700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>700</v>
-      </c>
-      <c r="F48" s="3">
-        <v>800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>800</v>
       </c>
       <c r="H48" s="3">
         <v>800</v>
@@ -2401,20 +2616,20 @@
         <v>800</v>
       </c>
       <c r="J48" s="3">
+        <v>800</v>
+      </c>
+      <c r="K48" s="3">
+        <v>800</v>
+      </c>
+      <c r="L48" s="3">
         <v>1400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1800</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2424,8 +2639,14 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2471,8 +2692,14 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2518,8 +2745,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2565,8 +2798,14 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2576,11 +2815,11 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
-        <v>100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -2597,11 +2836,11 @@
       <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
+        <v>100</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2612,8 +2851,14 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2659,44 +2904,50 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>19600</v>
+      </c>
+      <c r="F54" s="3">
         <v>12700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>12700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>13100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>13100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>11100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>9100</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2706,8 +2957,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2725,8 +2982,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2744,44 +3003,46 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>300</v>
+      </c>
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,44 +3052,50 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>700</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2838,44 +3105,50 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F59" s="3">
         <v>1600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2885,44 +3158,50 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F60" s="3">
         <v>4400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2932,44 +3211,50 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F61" s="3">
         <v>1300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -2979,8 +3264,14 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3026,8 +3317,14 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3073,8 +3370,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3120,8 +3423,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3167,44 +3476,50 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F66" s="3">
         <v>5700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>7100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>6400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>6300</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3214,8 +3529,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3233,8 +3554,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3280,8 +3603,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3327,8 +3656,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3374,8 +3709,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3421,44 +3762,50 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F72" s="3">
         <v>1600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2700</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3468,8 +3815,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3515,8 +3868,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3562,8 +3921,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3609,44 +3974,50 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F76" s="3">
         <v>7000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>7000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>6200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2700</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3656,8 +4027,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3703,49 +4080,55 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3755,44 +4138,50 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>200</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3802,8 +4191,14 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3821,8 +4216,10 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3839,10 +4236,10 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -3850,11 +4247,11 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3868,8 +4265,14 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3915,8 +4318,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3962,8 +4371,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4009,8 +4424,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4056,8 +4477,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4103,44 +4530,50 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F89" s="3">
         <v>1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4150,8 +4583,14 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4169,8 +4608,10 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4186,11 +4627,11 @@
       <c r="G91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -4216,8 +4657,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4263,8 +4710,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4310,43 +4763,49 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>1000</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4357,8 +4816,14 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4376,8 +4841,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4408,11 +4875,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -4423,8 +4890,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4470,8 +4943,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4517,8 +4996,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4564,28 +5049,34 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>2100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2100</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>-100</v>
@@ -4594,14 +5085,14 @@
         <v>-100</v>
       </c>
       <c r="L100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4611,8 +5102,14 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4623,28 +5120,28 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -4658,44 +5155,50 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,6 +5206,12 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGCB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGCB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
   <si>
     <t>LGCB</t>
   </si>
@@ -656,77 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -736,50 +738,56 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>800</v>
+      </c>
+      <c r="F8" s="3">
         <v>1800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>4500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>6800</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -789,50 +797,56 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>300</v>
+      </c>
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>5800</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -842,49 +856,55 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>500</v>
+      </c>
+      <c r="F10" s="3">
         <v>1300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>400</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
       <c r="L10" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3">
         <v>1000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1000</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
@@ -895,8 +915,14 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -916,50 +942,52 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>200</v>
+      </c>
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
       <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -969,8 +997,14 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1022,8 +1056,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1045,24 +1085,24 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1075,8 +1115,14 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1128,8 +1174,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1146,50 +1198,52 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F17" s="3">
         <v>2600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>3200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6500</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1199,49 +1253,55 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-700</v>
-      </c>
-      <c r="L18" s="3">
-        <v>300</v>
-      </c>
-      <c r="M18" s="3">
-        <v>300</v>
       </c>
       <c r="N18" s="3">
         <v>300</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
+      <c r="O18" s="3">
+        <v>300</v>
+      </c>
+      <c r="P18" s="3">
+        <v>300</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
@@ -1252,8 +1312,14 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1273,23 +1339,25 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1311,11 +1379,11 @@
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1326,50 +1394,56 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>300</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1379,23 +1453,29 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>500</v>
+      </c>
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
@@ -1417,11 +1497,11 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1432,28 +1512,34 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-800</v>
       </c>
       <c r="J23" s="3">
         <v>-800</v>
@@ -1462,20 +1548,20 @@
         <v>-800</v>
       </c>
       <c r="L23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N23" s="3">
         <v>400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>300</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1485,49 +1571,55 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
-      </c>
-      <c r="L24" s="3">
-        <v>100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="O24" s="3">
+        <v>100</v>
+      </c>
+      <c r="P24" s="3">
+        <v>100</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
@@ -1538,8 +1630,14 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1591,50 +1689,56 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>200</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1644,50 +1748,56 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>200</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1697,8 +1807,14 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1750,8 +1866,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1803,8 +1925,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1856,8 +1984,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1909,23 +2043,29 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -1947,11 +2087,11 @@
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -1962,50 +2102,56 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>200</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2015,8 +2161,14 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2068,50 +2220,56 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>200</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,55 +2279,61 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2179,8 +2343,14 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2200,8 +2370,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2221,50 +2393,52 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>700</v>
+      </c>
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3700</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2274,28 +2448,34 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>400</v>
-      </c>
-      <c r="H42" s="3">
-        <v>200</v>
-      </c>
-      <c r="I42" s="3">
-        <v>200</v>
       </c>
       <c r="J42" s="3">
         <v>200</v>
@@ -2304,20 +2484,20 @@
         <v>200</v>
       </c>
       <c r="L42" s="3">
+        <v>200</v>
+      </c>
+      <c r="M42" s="3">
+        <v>200</v>
+      </c>
+      <c r="N42" s="3">
         <v>100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>200</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -2327,50 +2507,56 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F43" s="3">
         <v>16100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>16100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>7100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>7100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2700</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2380,8 +2566,14 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2392,10 +2584,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H44" s="3">
         <v>100</v>
@@ -2404,26 +2596,26 @@
         <v>100</v>
       </c>
       <c r="J44" s="3">
+        <v>100</v>
+      </c>
+      <c r="K44" s="3">
+        <v>100</v>
+      </c>
+      <c r="L44" s="3">
         <v>700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>300</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2433,50 +2625,56 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F45" s="3">
         <v>2300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>5200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>5100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>5100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2486,50 +2684,56 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F46" s="3">
         <v>19000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>19000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>12000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>12000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>11900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>9600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>9200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>9200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>7100</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2539,8 +2743,14 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2568,21 +2778,21 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2592,8 +2802,14 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2604,16 +2820,16 @@
         <v>600</v>
       </c>
       <c r="F48" s="3">
+        <v>600</v>
+      </c>
+      <c r="G48" s="3">
+        <v>600</v>
+      </c>
+      <c r="H48" s="3">
         <v>700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>700</v>
-      </c>
-      <c r="H48" s="3">
-        <v>800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>800</v>
       </c>
       <c r="J48" s="3">
         <v>800</v>
@@ -2622,20 +2838,20 @@
         <v>800</v>
       </c>
       <c r="L48" s="3">
+        <v>800</v>
+      </c>
+      <c r="M48" s="3">
+        <v>800</v>
+      </c>
+      <c r="N48" s="3">
         <v>1400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,8 +2861,14 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2698,8 +2920,14 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2751,8 +2979,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2804,8 +3038,14 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2821,11 +3061,11 @@
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
-        <v>100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -2842,11 +3082,11 @@
       <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>100</v>
+      </c>
+      <c r="P52" s="3">
+        <v>100</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -2857,8 +3097,14 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2910,50 +3156,56 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>21400</v>
+      </c>
+      <c r="F54" s="3">
         <v>19600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>19600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>12700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>12700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>13100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>13100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>10600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>10600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9100</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2963,8 +3215,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2984,8 +3242,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3005,50 +3265,52 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3058,50 +3320,56 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F58" s="3">
         <v>8300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>8300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>700</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3111,50 +3379,56 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3164,50 +3438,56 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F60" s="3">
         <v>11600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>11600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3700</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,50 +3497,56 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>900</v>
+      </c>
+      <c r="F61" s="3">
         <v>1100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3270,8 +3556,14 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3323,8 +3615,14 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3376,8 +3674,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3429,8 +3733,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3482,50 +3792,56 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F66" s="3">
         <v>12600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>7100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>7100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>6400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6300</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,8 +3851,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3556,8 +3878,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3609,8 +3933,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3662,8 +3992,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3715,8 +4051,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3768,50 +4110,56 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2700</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3821,8 +4169,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3874,8 +4228,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3927,8 +4287,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3980,50 +4346,56 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16300</v>
+      </c>
+      <c r="F76" s="3">
         <v>6900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>7000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>7000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2700</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4033,8 +4405,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4086,55 +4464,61 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4144,50 +4528,56 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>200</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4197,8 +4587,14 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4218,8 +4614,10 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4242,10 +4640,10 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -4253,11 +4651,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -4271,8 +4669,14 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4324,8 +4728,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4377,8 +4787,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4430,8 +4846,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4483,8 +4905,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4536,50 +4964,56 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4589,8 +5023,14 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4610,16 +5050,18 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -4633,11 +5075,11 @@
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4663,8 +5105,14 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4716,8 +5164,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4769,49 +5223,55 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-4400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>1000</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -4822,8 +5282,14 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4843,8 +5309,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4881,11 +5349,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -4896,8 +5364,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4949,8 +5423,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5002,8 +5482,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5055,34 +5541,40 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F100" s="3">
         <v>4400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>4400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>2100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2100</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
@@ -5091,14 +5583,14 @@
         <v>-100</v>
       </c>
       <c r="N100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5108,8 +5600,14 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5126,28 +5624,28 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -5161,50 +5659,56 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5212,6 +5716,12 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
